--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126317925</v>
       </c>
       <c r="B2" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126317934</v>
       </c>
       <c r="B3" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126317941</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126317923</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>126317926</v>
       </c>
       <c r="B6" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>126317939</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>126317937</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126317935</v>
+        <v>126317940</v>
       </c>
       <c r="B9" t="n">
-        <v>91256</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761889</v>
+        <v>761893</v>
       </c>
       <c r="R9" t="n">
-        <v>7180687</v>
+        <v>7180686</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126317940</v>
+        <v>126317935</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>91260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761893</v>
+        <v>761889</v>
       </c>
       <c r="R10" t="n">
-        <v>7180686</v>
+        <v>7180687</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
         <v>126317928</v>
       </c>
       <c r="B11" t="n">
-        <v>98366</v>
+        <v>98370</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>126317936</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>126317931</v>
       </c>
       <c r="B13" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126317933</v>
+        <v>126317924</v>
       </c>
       <c r="B14" t="n">
-        <v>98345</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761844</v>
+        <v>761956</v>
       </c>
       <c r="R14" t="n">
-        <v>7180530</v>
+        <v>7180751</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,6 +1915,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126317924</v>
+        <v>126317933</v>
       </c>
       <c r="B15" t="n">
-        <v>57652</v>
+        <v>98349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761956</v>
+        <v>761844</v>
       </c>
       <c r="R15" t="n">
-        <v>7180751</v>
+        <v>7180530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2012,11 +2017,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2046,7 +2046,7 @@
         <v>126317920</v>
       </c>
       <c r="B16" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>126317922</v>
       </c>
       <c r="B17" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>126317921</v>
       </c>
       <c r="B18" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>126317930</v>
       </c>
       <c r="B19" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>126317932</v>
       </c>
       <c r="B20" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>126317929</v>
       </c>
       <c r="B21" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>126317942</v>
       </c>
       <c r="B22" t="n">
-        <v>88647</v>
+        <v>88651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>126317919</v>
       </c>
       <c r="B23" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126317925</v>
+        <v>126317934</v>
       </c>
       <c r="B2" t="n">
-        <v>80109</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761885</v>
+        <v>761836</v>
       </c>
       <c r="R2" t="n">
-        <v>7180706</v>
+        <v>7180586</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126317934</v>
+        <v>126317925</v>
       </c>
       <c r="B3" t="n">
-        <v>98349</v>
+        <v>80109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761836</v>
+        <v>761885</v>
       </c>
       <c r="R3" t="n">
-        <v>7180586</v>
+        <v>7180706</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>126317926</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126317937</v>
+        <v>126317935</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761858</v>
+        <v>761889</v>
       </c>
       <c r="R8" t="n">
-        <v>7180633</v>
+        <v>7180687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126317940</v>
+        <v>126317937</v>
       </c>
       <c r="B9" t="n">
         <v>78977</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761893</v>
+        <v>761858</v>
       </c>
       <c r="R9" t="n">
-        <v>7180686</v>
+        <v>7180633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126317935</v>
+        <v>126317940</v>
       </c>
       <c r="B10" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761889</v>
+        <v>761893</v>
       </c>
       <c r="R10" t="n">
-        <v>7180687</v>
+        <v>7180686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
         <v>126317928</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126317924</v>
+        <v>126317933</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761956</v>
+        <v>761844</v>
       </c>
       <c r="R14" t="n">
-        <v>7180751</v>
+        <v>7180530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,11 +1915,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126317933</v>
+        <v>126317924</v>
       </c>
       <c r="B15" t="n">
-        <v>98349</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761844</v>
+        <v>761956</v>
       </c>
       <c r="R15" t="n">
-        <v>7180530</v>
+        <v>7180751</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2017,6 +2012,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2449,7 +2449,7 @@
         <v>126317932</v>
       </c>
       <c r="B20" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126317934</v>
+        <v>126317925</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>80109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761836</v>
+        <v>761885</v>
       </c>
       <c r="R2" t="n">
-        <v>7180586</v>
+        <v>7180706</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126317925</v>
+        <v>126317934</v>
       </c>
       <c r="B3" t="n">
-        <v>80109</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761885</v>
+        <v>761836</v>
       </c>
       <c r="R3" t="n">
-        <v>7180706</v>
+        <v>7180586</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126317933</v>
+        <v>126317924</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761844</v>
+        <v>761956</v>
       </c>
       <c r="R14" t="n">
-        <v>7180530</v>
+        <v>7180751</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,6 +1915,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126317924</v>
+        <v>126317933</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761956</v>
+        <v>761844</v>
       </c>
       <c r="R15" t="n">
-        <v>7180751</v>
+        <v>7180530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2012,11 +2017,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126317930</v>
+        <v>126317932</v>
       </c>
       <c r="B19" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761884</v>
+        <v>761895</v>
       </c>
       <c r="R19" t="n">
-        <v>7180704</v>
+        <v>7180574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126317932</v>
+        <v>126317930</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761895</v>
+        <v>761884</v>
       </c>
       <c r="R20" t="n">
-        <v>7180574</v>
+        <v>7180704</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126317942</v>
+        <v>126317919</v>
       </c>
       <c r="B22" t="n">
-        <v>88651</v>
+        <v>57656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>761925</v>
+        <v>761859</v>
       </c>
       <c r="R22" t="n">
-        <v>7180585</v>
+        <v>7180543</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2711,6 +2711,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2737,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126317919</v>
+        <v>126317942</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>88651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,21 +2753,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2772,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>761859</v>
+        <v>761925</v>
       </c>
       <c r="R23" t="n">
-        <v>7180543</v>
+        <v>7180585</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,11 +2813,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126317925</v>
+        <v>126317934</v>
       </c>
       <c r="B2" t="n">
-        <v>80109</v>
+        <v>98352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761885</v>
+        <v>761836</v>
       </c>
       <c r="R2" t="n">
-        <v>7180706</v>
+        <v>7180586</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126317934</v>
+        <v>126317925</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>80109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761836</v>
+        <v>761885</v>
       </c>
       <c r="R3" t="n">
-        <v>7180586</v>
+        <v>7180706</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -2349,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126317932</v>
+        <v>126317930</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761895</v>
+        <v>761884</v>
       </c>
       <c r="R19" t="n">
-        <v>7180574</v>
+        <v>7180704</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126317930</v>
+        <v>126317932</v>
       </c>
       <c r="B20" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761884</v>
+        <v>761895</v>
       </c>
       <c r="R20" t="n">
-        <v>7180704</v>
+        <v>7180574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2640,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>126317919</v>
+        <v>126317942</v>
       </c>
       <c r="B22" t="n">
-        <v>57656</v>
+        <v>88651</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,21 +2651,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>761859</v>
+        <v>761925</v>
       </c>
       <c r="R22" t="n">
-        <v>7180543</v>
+        <v>7180585</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2711,11 +2711,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>126317942</v>
+        <v>126317919</v>
       </c>
       <c r="B23" t="n">
-        <v>88651</v>
+        <v>57656</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2753,21 +2748,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>761925</v>
+        <v>761859</v>
       </c>
       <c r="R23" t="n">
-        <v>7180585</v>
+        <v>7180543</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,6 +2808,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126317934</v>
+        <v>126317925</v>
       </c>
       <c r="B2" t="n">
-        <v>98352</v>
+        <v>80109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761836</v>
+        <v>761885</v>
       </c>
       <c r="R2" t="n">
-        <v>7180586</v>
+        <v>7180706</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126317925</v>
+        <v>126317934</v>
       </c>
       <c r="B3" t="n">
-        <v>80109</v>
+        <v>98352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761885</v>
+        <v>761836</v>
       </c>
       <c r="R3" t="n">
-        <v>7180706</v>
+        <v>7180586</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126317935</v>
+        <v>126317937</v>
       </c>
       <c r="B8" t="n">
-        <v>91260</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761889</v>
+        <v>761858</v>
       </c>
       <c r="R8" t="n">
-        <v>7180687</v>
+        <v>7180633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126317937</v>
+        <v>126317940</v>
       </c>
       <c r="B9" t="n">
         <v>78977</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761858</v>
+        <v>761893</v>
       </c>
       <c r="R9" t="n">
-        <v>7180633</v>
+        <v>7180686</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126317940</v>
+        <v>126317935</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>91260</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761893</v>
+        <v>761889</v>
       </c>
       <c r="R10" t="n">
-        <v>7180686</v>
+        <v>7180687</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126317924</v>
+        <v>126317933</v>
       </c>
       <c r="B14" t="n">
-        <v>57656</v>
+        <v>98352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761956</v>
+        <v>761844</v>
       </c>
       <c r="R14" t="n">
-        <v>7180751</v>
+        <v>7180530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,11 +1915,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126317933</v>
+        <v>126317924</v>
       </c>
       <c r="B15" t="n">
-        <v>98352</v>
+        <v>57656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761844</v>
+        <v>761956</v>
       </c>
       <c r="R15" t="n">
-        <v>7180530</v>
+        <v>7180751</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2017,6 +2012,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126317930</v>
+        <v>126317932</v>
       </c>
       <c r="B19" t="n">
-        <v>80080</v>
+        <v>98352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761884</v>
+        <v>761895</v>
       </c>
       <c r="R19" t="n">
-        <v>7180704</v>
+        <v>7180574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126317932</v>
+        <v>126317930</v>
       </c>
       <c r="B20" t="n">
-        <v>98352</v>
+        <v>80080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761895</v>
+        <v>761884</v>
       </c>
       <c r="R20" t="n">
-        <v>7180574</v>
+        <v>7180704</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126317925</v>
       </c>
       <c r="B2" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126317934</v>
       </c>
       <c r="B3" t="n">
-        <v>98352</v>
+        <v>98361</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126317941</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>126317923</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>126317926</v>
       </c>
       <c r="B6" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>126317939</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126317937</v>
+        <v>126317935</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>91263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761858</v>
+        <v>761889</v>
       </c>
       <c r="R8" t="n">
-        <v>7180633</v>
+        <v>7180687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126317940</v>
+        <v>126317937</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>78980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761893</v>
+        <v>761858</v>
       </c>
       <c r="R9" t="n">
-        <v>7180686</v>
+        <v>7180633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126317935</v>
+        <v>126317940</v>
       </c>
       <c r="B10" t="n">
-        <v>91260</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761889</v>
+        <v>761893</v>
       </c>
       <c r="R10" t="n">
-        <v>7180687</v>
+        <v>7180686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1556,7 +1556,7 @@
         <v>126317928</v>
       </c>
       <c r="B11" t="n">
-        <v>98373</v>
+        <v>98382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126317936</v>
+        <v>126317931</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>80083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761833</v>
+        <v>761888</v>
       </c>
       <c r="R12" t="n">
-        <v>7180594</v>
+        <v>7180710</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126317931</v>
+        <v>126317936</v>
       </c>
       <c r="B13" t="n">
-        <v>80080</v>
+        <v>78980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761888</v>
+        <v>761833</v>
       </c>
       <c r="R13" t="n">
-        <v>7180710</v>
+        <v>7180594</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126317933</v>
+        <v>126317924</v>
       </c>
       <c r="B14" t="n">
-        <v>98352</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761844</v>
+        <v>761956</v>
       </c>
       <c r="R14" t="n">
-        <v>7180530</v>
+        <v>7180751</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,6 +1915,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126317924</v>
+        <v>126317933</v>
       </c>
       <c r="B15" t="n">
-        <v>57656</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761956</v>
+        <v>761844</v>
       </c>
       <c r="R15" t="n">
-        <v>7180751</v>
+        <v>7180530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2012,11 +2017,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2046,7 +2046,7 @@
         <v>126317920</v>
       </c>
       <c r="B16" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>126317922</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>126317921</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2349,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126317932</v>
+        <v>126317930</v>
       </c>
       <c r="B19" t="n">
-        <v>98352</v>
+        <v>80083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761895</v>
+        <v>761884</v>
       </c>
       <c r="R19" t="n">
-        <v>7180574</v>
+        <v>7180704</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126317930</v>
+        <v>126317932</v>
       </c>
       <c r="B20" t="n">
-        <v>80080</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761884</v>
+        <v>761895</v>
       </c>
       <c r="R20" t="n">
-        <v>7180704</v>
+        <v>7180574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2546,7 +2546,7 @@
         <v>126317929</v>
       </c>
       <c r="B21" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2643,7 +2643,7 @@
         <v>126317942</v>
       </c>
       <c r="B22" t="n">
-        <v>88651</v>
+        <v>88654</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>126317919</v>
       </c>
       <c r="B23" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126317931</v>
+        <v>126317936</v>
       </c>
       <c r="B12" t="n">
-        <v>80083</v>
+        <v>78980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>761888</v>
+        <v>761833</v>
       </c>
       <c r="R12" t="n">
-        <v>7180710</v>
+        <v>7180594</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126317936</v>
+        <v>126317931</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>80083</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>761833</v>
+        <v>761888</v>
       </c>
       <c r="R13" t="n">
-        <v>7180594</v>
+        <v>7180710</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126317924</v>
+        <v>126317933</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761956</v>
+        <v>761844</v>
       </c>
       <c r="R14" t="n">
-        <v>7180751</v>
+        <v>7180530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,11 +1915,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126317933</v>
+        <v>126317924</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761844</v>
+        <v>761956</v>
       </c>
       <c r="R15" t="n">
-        <v>7180530</v>
+        <v>7180751</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2017,6 +2012,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126317930</v>
+        <v>126317932</v>
       </c>
       <c r="B19" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761884</v>
+        <v>761895</v>
       </c>
       <c r="R19" t="n">
-        <v>7180704</v>
+        <v>7180574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126317932</v>
+        <v>126317930</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761895</v>
+        <v>761884</v>
       </c>
       <c r="R20" t="n">
-        <v>7180574</v>
+        <v>7180704</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126317935</v>
+        <v>126317937</v>
       </c>
       <c r="B8" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761889</v>
+        <v>761858</v>
       </c>
       <c r="R8" t="n">
-        <v>7180687</v>
+        <v>7180633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126317937</v>
+        <v>126317940</v>
       </c>
       <c r="B9" t="n">
         <v>78980</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761858</v>
+        <v>761893</v>
       </c>
       <c r="R9" t="n">
-        <v>7180633</v>
+        <v>7180686</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126317940</v>
+        <v>126317935</v>
       </c>
       <c r="B10" t="n">
-        <v>78980</v>
+        <v>91263</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761893</v>
+        <v>761889</v>
       </c>
       <c r="R10" t="n">
-        <v>7180686</v>
+        <v>7180687</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126317933</v>
+        <v>126317924</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761844</v>
+        <v>761956</v>
       </c>
       <c r="R14" t="n">
-        <v>7180530</v>
+        <v>7180751</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,6 +1915,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126317924</v>
+        <v>126317933</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761956</v>
+        <v>761844</v>
       </c>
       <c r="R15" t="n">
-        <v>7180751</v>
+        <v>7180530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2012,11 +2017,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126317932</v>
+        <v>126317930</v>
       </c>
       <c r="B19" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761895</v>
+        <v>761884</v>
       </c>
       <c r="R19" t="n">
-        <v>7180574</v>
+        <v>7180704</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126317930</v>
+        <v>126317932</v>
       </c>
       <c r="B20" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761884</v>
+        <v>761895</v>
       </c>
       <c r="R20" t="n">
-        <v>7180704</v>
+        <v>7180574</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126317925</v>
+        <v>126317934</v>
       </c>
       <c r="B2" t="n">
-        <v>80112</v>
+        <v>98361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>761885</v>
+        <v>761836</v>
       </c>
       <c r="R2" t="n">
-        <v>7180706</v>
+        <v>7180586</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126317934</v>
+        <v>126317925</v>
       </c>
       <c r="B3" t="n">
-        <v>98361</v>
+        <v>80112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>761836</v>
+        <v>761885</v>
       </c>
       <c r="R3" t="n">
-        <v>7180586</v>
+        <v>7180706</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126317924</v>
+        <v>126317933</v>
       </c>
       <c r="B14" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761956</v>
+        <v>761844</v>
       </c>
       <c r="R14" t="n">
-        <v>7180751</v>
+        <v>7180530</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,11 +1915,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1946,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126317933</v>
+        <v>126317924</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1981,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761844</v>
+        <v>761956</v>
       </c>
       <c r="R15" t="n">
-        <v>7180530</v>
+        <v>7180751</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2017,6 +2012,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 12353-2025 artfynd.xlsx
+++ b/artfynd/A 12353-2025 artfynd.xlsx
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126317937</v>
+        <v>126317935</v>
       </c>
       <c r="B8" t="n">
-        <v>78980</v>
+        <v>91263</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>761858</v>
+        <v>761889</v>
       </c>
       <c r="R8" t="n">
-        <v>7180633</v>
+        <v>7180687</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126317940</v>
+        <v>126317937</v>
       </c>
       <c r="B9" t="n">
         <v>78980</v>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>761893</v>
+        <v>761858</v>
       </c>
       <c r="R9" t="n">
-        <v>7180686</v>
+        <v>7180633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126317935</v>
+        <v>126317940</v>
       </c>
       <c r="B10" t="n">
-        <v>91263</v>
+        <v>78980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>761889</v>
+        <v>761893</v>
       </c>
       <c r="R10" t="n">
-        <v>7180687</v>
+        <v>7180686</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126317933</v>
+        <v>126317924</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>57657</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>761844</v>
+        <v>761956</v>
       </c>
       <c r="R14" t="n">
-        <v>7180530</v>
+        <v>7180751</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1915,6 +1915,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-06-30</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1941,32 +1946,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126317924</v>
+        <v>126317933</v>
       </c>
       <c r="B15" t="n">
-        <v>57657</v>
+        <v>98361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1981,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>761956</v>
+        <v>761844</v>
       </c>
       <c r="R15" t="n">
-        <v>7180751</v>
+        <v>7180530</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2012,11 +2017,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-06-30</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2349,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126317930</v>
+        <v>126317932</v>
       </c>
       <c r="B19" t="n">
-        <v>80083</v>
+        <v>98361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>761884</v>
+        <v>761895</v>
       </c>
       <c r="R19" t="n">
-        <v>7180704</v>
+        <v>7180574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126317932</v>
+        <v>126317930</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>80083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>761895</v>
+        <v>761884</v>
       </c>
       <c r="R20" t="n">
-        <v>7180574</v>
+        <v>7180704</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
